--- a/ARM Functions/Battle.cro function calls.xlsx
+++ b/ARM Functions/Battle.cro function calls.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BF4649-856B-4D3D-A511-C52C9341DB91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A60F283-3E05-4CCD-AC95-E2EE27213B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16457" yWindow="0" windowWidth="16457" windowHeight="17914" firstSheet="2" activeTab="6" xr2:uid="{F2BF6E18-7729-4466-960B-32E8A7D80BFA}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" firstSheet="2" activeTab="6" xr2:uid="{F2BF6E18-7729-4466-960B-32E8A7D80BFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Battle.cro function call change" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4513" uniqueCount="3370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4540" uniqueCount="3368">
   <si>
     <t>01</t>
   </si>
@@ -10116,12 +10116,6 @@
   </si>
   <si>
     <t>Identified</t>
-  </si>
-  <si>
-    <t>Ef</t>
-  </si>
-  <si>
-    <t>7e</t>
   </si>
   <si>
     <t>007E1238</t>
@@ -11046,13 +11040,13 @@
         <v>3309</v>
       </c>
       <c r="P1" s="23" t="s">
-        <v>3362</v>
+        <v>3360</v>
       </c>
       <c r="Q1" s="24" t="s">
         <v>3309</v>
       </c>
       <c r="R1" s="23" t="s">
-        <v>3363</v>
+        <v>3361</v>
       </c>
       <c r="S1" s="24" t="s">
         <v>3309</v>
@@ -11157,7 +11151,7 @@
         <v>172</v>
       </c>
       <c r="R4" s="26" t="s">
-        <v>3360</v>
+        <v>3358</v>
       </c>
       <c r="S4" s="16" t="s">
         <v>300</v>
@@ -11196,11 +11190,11 @@
       </c>
       <c r="O5" s="18"/>
       <c r="P5" s="17" t="s">
-        <v>3361</v>
+        <v>3359</v>
       </c>
       <c r="Q5" s="18"/>
       <c r="R5" s="17" t="s">
-        <v>3364</v>
+        <v>3362</v>
       </c>
       <c r="S5" s="18"/>
     </row>
@@ -11730,7 +11724,7 @@
         <v>2455</v>
       </c>
       <c r="J11" t="s">
-        <v>3367</v>
+        <v>3365</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="0"/>
@@ -11767,7 +11761,7 @@
         <v>2487</v>
       </c>
       <c r="J12" t="s">
-        <v>3365</v>
+        <v>3363</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
@@ -11804,7 +11798,7 @@
         <v>185</v>
       </c>
       <c r="J13" t="s">
-        <v>3366</v>
+        <v>3364</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="0"/>
@@ -11986,7 +11980,7 @@
         <v>143</v>
       </c>
       <c r="J18" t="s">
-        <v>3368</v>
+        <v>3366</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="0"/>
@@ -29107,7 +29101,7 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="6" t="s">
-        <v>3360</v>
+        <v>3358</v>
       </c>
       <c r="B14" s="6" t="str">
         <f>DEC2HEX(HEX2DEC(A14)-'Ability Index'!$T$1,8)</f>
@@ -33174,6 +33168,9 @@
         <f t="shared" si="16"/>
         <v>cro</v>
       </c>
+      <c r="J69" s="7" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" s="4" t="str">
@@ -36196,7 +36193,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:12">
       <c r="A145" s="4" t="str">
         <f t="shared" si="28"/>
         <v>007E0634</v>
@@ -36237,7 +36234,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:12">
       <c r="A146" s="4" t="str">
         <f t="shared" si="28"/>
         <v>007E063C</v>
@@ -36278,7 +36275,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:12">
       <c r="A147" s="4" t="str">
         <f t="shared" si="28"/>
         <v>007E0644</v>
@@ -36319,7 +36316,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:12">
       <c r="A148" s="4" t="str">
         <f t="shared" si="28"/>
         <v>007E064C</v>
@@ -36360,7 +36357,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:12">
       <c r="A149" s="4" t="str">
         <f t="shared" si="28"/>
         <v>007E0654</v>
@@ -36401,7 +36398,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:12">
       <c r="A150" s="4" t="str">
         <f t="shared" si="28"/>
         <v>007E065C</v>
@@ -36438,8 +36435,17 @@
         <f t="shared" si="27"/>
         <v>cro</v>
       </c>
-    </row>
-    <row r="151" spans="1:11">
+      <c r="J150" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="K150" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="L150" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12">
       <c r="A151" s="4" t="str">
         <f t="shared" si="28"/>
         <v>007E0664</v>
@@ -36480,7 +36486,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:12">
       <c r="A152" s="4" t="str">
         <f t="shared" si="28"/>
         <v>007E066C</v>
@@ -36521,7 +36527,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:12">
       <c r="A153" s="4" t="str">
         <f t="shared" si="28"/>
         <v>007E0674</v>
@@ -36562,7 +36568,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:12">
       <c r="A154" s="4" t="str">
         <f t="shared" si="28"/>
         <v>007E067C</v>
@@ -36606,7 +36612,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:12">
       <c r="A155" s="4" t="str">
         <f t="shared" si="28"/>
         <v>007E0684</v>
@@ -36644,7 +36650,7 @@
         <v>cro</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:12">
       <c r="A156" s="4" t="str">
         <f t="shared" si="28"/>
         <v>007E068C</v>
@@ -36688,7 +36694,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:12">
       <c r="A157" s="4" t="str">
         <f t="shared" si="28"/>
         <v>007E0694</v>
@@ -36726,7 +36732,7 @@
         <v>cro</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:12">
       <c r="A158" s="4" t="str">
         <f t="shared" si="28"/>
         <v>007E069C</v>
@@ -36764,7 +36770,7 @@
         <v>cro</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:12">
       <c r="A159" s="4" t="str">
         <f t="shared" si="28"/>
         <v>007E06A4</v>
@@ -36802,7 +36808,7 @@
         <v>cro</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:12">
       <c r="A160" s="4" t="str">
         <f t="shared" si="28"/>
         <v>007E06AC</v>
@@ -38159,7 +38165,7 @@
     <col min="6" max="6" width="15.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.2109375" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.35546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.7109375" style="4" customWidth="1"/>
     <col min="10" max="10" width="2.92578125" style="4" customWidth="1"/>
     <col min="11" max="14" width="2.92578125" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="17" width="2.7109375" style="4" bestFit="1" customWidth="1"/>
@@ -40534,6 +40540,9 @@
         <f t="shared" si="4"/>
         <v>cro</v>
       </c>
+      <c r="J56" s="4">
+        <v>47</v>
+      </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="4" t="str">
@@ -41579,7 +41588,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:15">
+    <row r="81" spans="1:19">
       <c r="A81" s="4" t="str">
         <f t="shared" si="16"/>
         <v>007E1988</v>
@@ -41635,7 +41644,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:15">
+    <row r="82" spans="1:19">
       <c r="A82" s="4" t="str">
         <f t="shared" si="16"/>
         <v>007E1990</v>
@@ -41685,7 +41694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:15">
+    <row r="83" spans="1:19">
       <c r="A83" s="4" t="str">
         <f t="shared" si="16"/>
         <v>007E1998</v>
@@ -41738,7 +41747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:15">
+    <row r="84" spans="1:19">
       <c r="A84" s="4" t="str">
         <f t="shared" si="16"/>
         <v>007E19A0</v>
@@ -41791,7 +41800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:15">
+    <row r="85" spans="1:19">
       <c r="A85" s="4" t="str">
         <f t="shared" si="16"/>
         <v>007E19A8</v>
@@ -41844,7 +41853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:15">
+    <row r="86" spans="1:19">
       <c r="A86" s="4" t="str">
         <f t="shared" si="16"/>
         <v>007E19B0</v>
@@ -41894,7 +41903,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:15">
+    <row r="87" spans="1:19">
       <c r="A87" s="4" t="str">
         <f t="shared" si="16"/>
         <v>007E19B8</v>
@@ -41935,7 +41944,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="88" spans="1:15">
+    <row r="88" spans="1:19">
       <c r="A88" s="4" t="str">
         <f t="shared" si="16"/>
         <v>007E19C0</v>
@@ -41982,7 +41991,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="89" spans="1:15">
+    <row r="89" spans="1:19">
       <c r="A89" s="4" t="str">
         <f t="shared" si="16"/>
         <v>007E19C8</v>
@@ -42019,8 +42028,38 @@
         <f t="shared" si="13"/>
         <v>cro</v>
       </c>
-    </row>
-    <row r="90" spans="1:15">
+      <c r="J89" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="L89" s="4">
+        <v>96</v>
+      </c>
+      <c r="M89" s="4">
+        <v>81</v>
+      </c>
+      <c r="N89" s="4">
+        <v>91</v>
+      </c>
+      <c r="O89" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="P89" s="4">
+        <v>90</v>
+      </c>
+      <c r="Q89" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="R89" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="S89" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19">
       <c r="A90" s="4" t="str">
         <f t="shared" si="16"/>
         <v>007E19D0</v>
@@ -42067,7 +42106,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="91" spans="1:15">
+    <row r="91" spans="1:19">
       <c r="A91" s="4" t="str">
         <f t="shared" si="16"/>
         <v>007E19D8</v>
@@ -42111,7 +42150,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="92" spans="1:15">
+    <row r="92" spans="1:19">
       <c r="A92" s="4" t="str">
         <f t="shared" si="16"/>
         <v>007E19E0</v>
@@ -42155,7 +42194,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="93" spans="1:15">
+    <row r="93" spans="1:19">
       <c r="A93" s="4" t="str">
         <f t="shared" si="16"/>
         <v>007E19E8</v>
@@ -42199,7 +42238,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="94" spans="1:15">
+    <row r="94" spans="1:19">
       <c r="A94" s="4" t="str">
         <f t="shared" si="16"/>
         <v>007E19F0</v>
@@ -42240,7 +42279,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="95" spans="1:15">
+    <row r="95" spans="1:19">
       <c r="A95" s="4" t="str">
         <f t="shared" si="16"/>
         <v>007E19F8</v>
@@ -42284,7 +42323,7 @@
         <v>3292</v>
       </c>
     </row>
-    <row r="96" spans="1:15">
+    <row r="96" spans="1:19">
       <c r="A96" s="4" t="str">
         <f t="shared" si="16"/>
         <v>007E1A00</v>
@@ -44769,6 +44808,12 @@
         <f t="shared" si="20"/>
         <v>cro</v>
       </c>
+      <c r="J153" s="4">
+        <v>11</v>
+      </c>
+      <c r="K153" s="4" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="4" t="str">
@@ -45137,7 +45182,7 @@
         <v>244</v>
       </c>
       <c r="M161" s="4" t="s">
-        <v>3359</v>
+        <v>248</v>
       </c>
       <c r="N161" s="4" t="s">
         <v>25</v>
@@ -49533,6 +49578,27 @@
         <f t="shared" si="5"/>
         <v>cro</v>
       </c>
+      <c r="J35" s="11" t="s">
+        <v>3326</v>
+      </c>
+      <c r="K35">
+        <v>25</v>
+      </c>
+      <c r="L35">
+        <v>26</v>
+      </c>
+      <c r="M35" t="s">
+        <v>376</v>
+      </c>
+      <c r="N35" t="s">
+        <v>180</v>
+      </c>
+      <c r="O35">
+        <v>45</v>
+      </c>
+      <c r="P35" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" t="str">
@@ -49703,8 +49769,20 @@
         <f t="shared" si="5"/>
         <v>cro</v>
       </c>
+      <c r="J39" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L39" t="s">
+        <v>282</v>
+      </c>
+      <c r="M39" t="s">
+        <v>244</v>
+      </c>
       <c r="N39" t="s">
-        <v>3358</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -49744,6 +49822,15 @@
         <f t="shared" si="5"/>
         <v>cro</v>
       </c>
+      <c r="J40" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L40" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" t="str">
@@ -49782,6 +49869,15 @@
         <f t="shared" si="5"/>
         <v>cro</v>
       </c>
+      <c r="J41" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L41" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" t="str">
@@ -52105,6 +52201,9 @@
         <f t="shared" si="15"/>
         <v>cro</v>
       </c>
+      <c r="J96" s="11" t="s">
+        <v>376</v>
+      </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="str">
@@ -55505,6 +55604,9 @@
       <c r="J179" s="11" t="s">
         <v>242</v>
       </c>
+      <c r="K179">
+        <v>78</v>
+      </c>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" t="str">
@@ -55546,6 +55648,9 @@
       <c r="J180" s="11" t="s">
         <v>242</v>
       </c>
+      <c r="K180">
+        <v>78</v>
+      </c>
     </row>
     <row r="181" spans="1:13">
       <c r="A181" t="str">
@@ -55587,6 +55692,9 @@
       <c r="J181" s="11" t="s">
         <v>242</v>
       </c>
+      <c r="K181">
+        <v>78</v>
+      </c>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" t="str">
@@ -55628,6 +55736,9 @@
       <c r="J182" s="11" t="s">
         <v>242</v>
       </c>
+      <c r="K182">
+        <v>78</v>
+      </c>
     </row>
     <row r="183" spans="1:13">
       <c r="A183" t="str">
@@ -55669,6 +55780,9 @@
       <c r="J183" s="11" t="s">
         <v>242</v>
       </c>
+      <c r="K183">
+        <v>78</v>
+      </c>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" t="str">
@@ -55710,6 +55824,9 @@
       <c r="J184" s="11" t="s">
         <v>242</v>
       </c>
+      <c r="K184">
+        <v>78</v>
+      </c>
     </row>
     <row r="185" spans="1:13">
       <c r="A185" t="str">
@@ -56308,6 +56425,9 @@
         <f t="shared" si="29"/>
         <v>cro</v>
       </c>
+      <c r="J198" s="11" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="199" spans="1:10">
       <c r="A199" t="str">
@@ -62119,7 +62239,7 @@
         <v>313</v>
       </c>
       <c r="T337" t="s">
-        <v>3369</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="338" spans="1:20">

--- a/ARM Functions/Battle.cro function calls.xlsx
+++ b/ARM Functions/Battle.cro function calls.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A60F283-3E05-4CCD-AC95-E2EE27213B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6122E3-DBE2-4B80-B7C9-9A2AD1622FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" firstSheet="2" activeTab="6" xr2:uid="{F2BF6E18-7729-4466-960B-32E8A7D80BFA}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Ability Index" sheetId="6" r:id="rId6"/>
     <sheet name="Move Index" sheetId="1" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4540" uniqueCount="3368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4549" uniqueCount="3368">
   <si>
     <t>01</t>
   </si>
@@ -32568,6 +32568,12 @@
         <f t="shared" si="10"/>
         <v>cro</v>
       </c>
+      <c r="J54" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="4" t="str">
@@ -32606,6 +32612,12 @@
         <f t="shared" si="10"/>
         <v>cro</v>
       </c>
+      <c r="J55" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="4" t="str">
@@ -32723,6 +32735,9 @@
         <f t="shared" si="10"/>
         <v>cro</v>
       </c>
+      <c r="J58" s="7" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="4" t="str">
@@ -33047,6 +33062,12 @@
       <c r="I66" s="6" t="str">
         <f t="shared" ref="I66:I97" si="16">IF(HEX2DEC(G66)&lt;$W$1,"code.bin","cro")</f>
         <v>cro</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="K66" s="7" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -44152,6 +44173,12 @@
         <f t="shared" si="20"/>
         <v>cro</v>
       </c>
+      <c r="J137" s="4">
+        <v>97</v>
+      </c>
+      <c r="K137" s="4" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="138" spans="1:11">
       <c r="A138" s="4" t="str">
@@ -52693,6 +52720,9 @@
         <f t="shared" si="15"/>
         <v>cro</v>
       </c>
+      <c r="J108" s="11" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="str">
